--- a/leads_output.xlsx
+++ b/leads_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,7 +509,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>careers@communitydentalme.org</t>
+          <t>Portland@CommunityDentalME.org</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>careers@communitydentalme.org</t>
+          <t>Portland@CommunityDentalME.org</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>communitydentalcenter@yahoo.com</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>careers@communitydentalme.org</t>
+          <t>Portland@CommunityDentalME.org</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -754,17 +754,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Maine Care Dental</t>
+          <t>PCHC - Dental Center</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+12072563117</t>
+          <t>+12079922152</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=100092033889341</t>
+          <t>http://pchc.com/locations/dental-center/</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/login/device-based/regular/login/?login_attempt=1&amp;next=https%3A%2F%2Fwww.facebook.com%2Fpeople%2FMaine-Care-Dental%2F100092033889341%2F</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.swellbox.com/pchc-wizard.html</t>
         </is>
       </c>
     </row>
@@ -806,42 +806,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Maine Dental Surgery Center</t>
+          <t>Maine Center for Dental Medicine</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+12078889440</t>
+          <t>+12074749503</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>http://www.communitydentalme.org/</t>
+          <t>http://www.dental-holistic.com/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>careers@communitydentalme.org</t>
+          <t>info@mainecdm.com</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/DentalHolistic</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/communitydentalme/</t>
+          <t>https://www.instagram.com/drimammohammed/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/community-dental/</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/drmohammedimam</t>
         </is>
       </c>
     </row>
@@ -858,17 +858,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PCHC - Dental Center</t>
+          <t>Maine Care Dental</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+12079922152</t>
+          <t>+12072563117</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>http://pchc.com/locations/dental-center/</t>
+          <t>https://www.facebook.com/profile.php?id=100092033889341</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/login/device-based/regular/login/?login_attempt=1&amp;next=https%3A%2F%2Fwww.facebook.com%2Fpeople%2FMaine-Care-Dental%2F100092033889341%2F</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.swellbox.com/pchc-wizard.html</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -910,22 +910,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Maine Center for Dental Medicine</t>
+          <t>Community Dental Lewiston</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>+12079922152</t>
+          <t>+12077777442</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>http://pchc.com/locations/dental-center/</t>
+          <t>http://www.communitydentalme.org/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Portland@CommunityDentalME.org</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -935,17 +935,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/communitydentalme/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/community-dental/</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.swellbox.com/pchc-wizard.html</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -962,37 +962,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Community Dental Lewiston</t>
+          <t>Northern Maine Dental</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>+12077777442</t>
+          <t>+12074929521</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>http://www.communitydentalme.org/</t>
+          <t>http://northernmainedental.com/</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>careers@communitydentalme.org</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/northernmainedental/</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/communitydentalme/</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/community-dental/</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1066,37 +1066,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mainely Teeth Dental Clinic</t>
+          <t>Maine Dentistry - Auburn</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>+12078089498</t>
+          <t>+12073125422</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://mainelyteeth.org/</t>
+          <t>https://mainedentistry.com/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>info@mdportland.com</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/MainelyTeeth</t>
+          <t>https://www.facebook.com/mainedentistryauburn/</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://instagram.com/mainely_teeth</t>
+          <t>https://www.instagram.com/maine_dentistry/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/maine-dentistry/</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1118,37 +1118,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Maine Dentistry - Auburn</t>
+          <t>Community Dental-Farmington</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>+12073125422</t>
+          <t>+12077792659</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://mainedentistry.com/</t>
+          <t>http://www.communitydentalme.org/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>info@mdportland.com</t>
+          <t>Portland@CommunityDentalME.org</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mainedentistryauburn/</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maine_dentistry/</t>
+          <t>https://www.instagram.com/communitydentalme/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/maine-dentistry/</t>
+          <t>https://www.linkedin.com/company/community-dental/</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1170,37 +1170,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Maine Dentistry - Portland</t>
+          <t>Mainely Teeth Dental Clinic</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>+12076077221</t>
+          <t>+12078089498</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.mainedentistry.com/</t>
+          <t>https://mainelyteeth.org/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>info@mdportland.com</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mainedentistryauburn/</t>
+          <t>https://www.facebook.com/MainelyTeeth</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maine_dentistry/</t>
+          <t>https://instagram.com/mainely_teeth</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/maine-dentistry/</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1222,37 +1222,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Community Dental-Farmington</t>
+          <t>Maine Tiny Dental</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>+12076077221</t>
+          <t>+12075000454</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.mainedentistry.com/</t>
+          <t>https://www.mainetinydental.com/</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>info@mdportland.com</t>
+          <t>mainetinydental@hushmail.com</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mainedentistryauburn/</t>
+          <t>https://www.facebook.com/stacey.wright.963?__cft__[0]=AZVX4tu9JRVUjwpjOwcub2s-uF1kLT21j8EbA4c-_mVJ1Vvltuyu7vXeJhEOLIBWbL3qwyVpBTDkoU-Cl9cXV5RP0hVSyZSiMFQxMGFuZonwTw&amp;__tn__=-]C%2CP-R</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maine_dentistry/</t>
+          <t>https://www.instagram.com/mainetinydental?utm_source=ig_web_button_share_sheet&amp;igsh=ZDNlZDc0MzIxNw==</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/maine-dentistry/</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1274,17 +1274,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northern Maine Dental</t>
+          <t>Southern Maine Family Dental</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>+12074929521</t>
+          <t>+12074390779</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>http://northernmainedental.com/</t>
+          <t>http://www.some.dental/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/northernmainedental/</t>
+          <t>https://www.facebook.com/kingstonfamilydental/</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1326,37 +1326,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Southern Maine Family Dental</t>
+          <t>Maine Dentistry - Portland</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>+12074390779</t>
+          <t>+12076077221</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>http://www.some.dental/</t>
+          <t>https://www.mainedentistry.com/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>info@mdportland.com</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/kingstonfamilydental/</t>
+          <t>https://www.facebook.com/mainedentistryauburn/</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/maine_dentistry/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/maine-dentistry/</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Maine Tiny Dental</t>
+          <t>Capital City Smiles &amp; Wellness</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>+12075000454</t>
+          <t>+12075609200</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.mainetinydental.com/</t>
+          <t>http://www.ccsmileswell.com/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>mainetinydental@hushmail.com</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/stacey.wright.963?__cft__[0]=AZVX4tu9JRVUjwpjOwcub2s-uF1kLT21j8EbA4c-_mVJ1Vvltuyu7vXeJhEOLIBWbL3qwyVpBTDkoU-Cl9cXV5RP0hVSyZSiMFQxMGFuZonwTw&amp;__tn__=-]C%2CP-R</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mainetinydental?utm_source=ig_web_button_share_sheet&amp;igsh=ZDNlZDc0MzIxNw==</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1430,32 +1430,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Progressive Dental Care</t>
+          <t>Belfast Dental Care</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>+12077731703</t>
+          <t>+12073383669</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>http://www.progressivedentalcare.com/</t>
+          <t>https://www.belfast-dentalcare.com/</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>smile@belfast-dentalcare.com</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/progressivedentalcare/</t>
+          <t>https://www.facebook.com/BelfastDentalCare/reviews</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/progressivedentalcare/</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1482,32 +1482,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central Maine Smiles</t>
+          <t>Progressive Dental Care</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>+12075643455</t>
+          <t>+12077731703</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>http://www.centralmainesmiles.com/</t>
+          <t>http://www.progressivedentalcare.com/</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>info@centralmainesmiles.com</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/SteinkeCarusodentalcare/</t>
+          <t>https://www.facebook.com/progressivedentalcare/</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/progressivedentalcare/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1534,22 +1534,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lifetime Dental Health</t>
+          <t>State Street Dental Care</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>+12073832418</t>
+          <t>+12076229215</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://lifetimedentalhealth.com/</t>
+          <t>https://statestreetdentalme.com/</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>info@lifetimedentalhealth.com</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1586,27 +1586,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belfast Dental Care</t>
+          <t>Complete Dentistry</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>+12073383669</t>
+          <t>+12076454994</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.belfast-dentalcare.com/</t>
+          <t>http://completedentistrymaine.com/</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>smile@belfast-dentalcare.com</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/BelfastDentalCare/reviews</t>
+          <t>https://www.facebook.com/completedentistrymaine/</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1638,32 +1638,32 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Androscoggin Dental Care</t>
+          <t>Lifetime Dental Health</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>+12077293911</t>
+          <t>+12073832418</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://androscoggindentalcare.com/?utm_source=GoogleMyBusiness&amp;utm_medium=organic</t>
+          <t>https://lifetimedentalhealth.com/</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>info@lifetimedentalhealth.com</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/androscoggindentalcare/</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/androscoggindentalcare/</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1690,37 +1690,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>State Street Dental Care</t>
+          <t>Maine Dentistry - Gray</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>+12076229215</t>
+          <t>+12076573553</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://statestreetdentalme.com/</t>
+          <t>https://mainedentistry.com/</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>info@mdportland.com</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/mainedentistryauburn/</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/maine_dentistry/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/maine-dentistry/</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1742,42 +1742,42 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Maine Dentistry - Gray</t>
+          <t>Evergreen Dental Associates</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>+12076573553</t>
+          <t>+12076220861</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://mainedentistry.com/</t>
+          <t>http://www.evergreendental.net/</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>info@mdportland.com</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mainedentistryauburn/</t>
+          <t>https://www.facebook.com/MaineDentist</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maine_dentistry/</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/maine-dentistry/</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/DentalEvergreen</t>
         </is>
       </c>
     </row>
@@ -1846,17 +1846,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Evergreen Dental Associates</t>
+          <t>Androscoggin Dental Care</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>+12076220861</t>
+          <t>+12077293911</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>http://www.evergreendental.net/</t>
+          <t>https://androscoggindentalcare.com/?utm_source=GoogleMyBusiness&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/MaineDentist</t>
+          <t>https://www.facebook.com/androscoggindentalcare/</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/androscoggindentalcare/</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://twitter.com/DentalEvergreen</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1898,17 +1898,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Complete Dentistry</t>
+          <t>Forest Falls Dental</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>+12076454994</t>
+          <t>+12078463966</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>http://completedentistrymaine.com/</t>
+          <t>https://www.forestfallsdental.com/?utm_source=GoogleMyBusiness&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/completedentistrymaine/</t>
+          <t>https://www.facebook.com/forestfallsdental/</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/forestfallsdentalme/</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1950,17 +1950,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Forest Falls Dental</t>
+          <t>Caring Hands of Maine Dental Center</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>+12078463966</t>
+          <t>+12076676789</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.forestfallsdental.com/?utm_source=GoogleMyBusiness&amp;utm_medium=organic</t>
+          <t>http://www.caringhandsofmaine.org/</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/forestfallsdental/</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forestfallsdentalme/</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2002,17 +2002,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Caring Hands of Maine Dental Center</t>
+          <t>Falmouth Dental Health</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>+12076676789</t>
+          <t>+12077812328</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>http://www.caringhandsofmaine.org/</t>
+          <t>http://www.falmouthdentalhealth.com/</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/FalmouthDentalHealth</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/falmouthdental/</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2054,37 +2054,37 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Falmouth Dental Health</t>
+          <t>Maine Dental Surgery Center</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>+12077812328</t>
+          <t>+12078889440</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>http://www.falmouthdentalhealth.com/</t>
+          <t>http://www.communitydentalme.org/</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Portland@CommunityDentalME.org</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/FalmouthDentalHealth</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/falmouthdental/</t>
+          <t>https://www.instagram.com/communitydentalme/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/community-dental/</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Falmouth Dental Arts</t>
+          <t>Park Street Dental</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>+12077815900</t>
+          <t>+12078662813</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>http://www.falmouthdentalarts.com/</t>
+          <t>http://www.160parkstreetdental.com/</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>info@falmouthdentalarts.com</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/FalmouthDentalArts</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/falmouthdentalarts/</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2158,32 +2158,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Twin Pines Extraction &amp; Denture Center</t>
+          <t>Falmouth Dental Arts</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>+12079922060</t>
+          <t>+12077815900</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://twinpinesextraction.com/</t>
+          <t>http://www.falmouthdentalarts.com/</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>info@falmouthdentalarts.com</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>http://www.facebook.com/Twin-Pines-Extraction-and-Denture-Center-106367488488918</t>
+          <t>https://www.facebook.com/FalmouthDentalArts</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/falmouthdentalarts/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2205,32 +2205,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Maine</t>
+          <t>Buhl</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pine Tree Dental Care</t>
+          <t>Today's Dental Care</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>+12077814216</t>
+          <t>+12085436511</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>http://www.pinetreedentalcare.com/</t>
+          <t>https://www.todaysdentalcarejerome.com/</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>info@pinetreedentalcare.com</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/pinetreedentalcare/</t>
+          <t>https://www.facebook.com/TodaysDentalCareBuhlIdaho</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/irina-babayan-dds-16863191/</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/JeromeDentist</t>
         </is>
       </c>
     </row>
@@ -2257,37 +2257,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Maine</t>
+          <t>Buhl</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Park Street Dental</t>
+          <t>Family Health Services</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>+12078662813</t>
+          <t>+12085438271</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>http://www.160parkstreetdental.com/</t>
+          <t>https://fhsid.org/locations/buhl/buhl-clinic/</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>info@160parkstreetdental.com</t>
+          <t>info@fhsid.org</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/fhsidaho</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/fhsid</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Today's Dental Care</t>
+          <t>Chris Minert DMD</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2366,32 +2366,32 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Family Health Services</t>
+          <t>Beautiful Smiles by Denture Center</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>+12085438271</t>
+          <t>+12088082747</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://fhsid.org/locations/buhl/buhl-clinic/</t>
+          <t>https://beautifulsmilesdenturecenter.com/</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>info@fhsid.org</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/fhsidaho</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fhsid</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chris Minert DMD</t>
+          <t>Dr. John H. Osterkamp, DDS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>+12085436511</t>
+          <t>+12085438907</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2452,110 +2452,6 @@
         </is>
       </c>
       <c r="J39" t="inlineStr">
-        <is>
-          <t>https://twitter.com/JeromeDentist</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Dental Clinic</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Buhl</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Beautiful Smiles by Denture Center</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>+12088082747</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>https://beautifulsmilesdenturecenter.com/</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Dental Clinic</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Buhl</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Dr. John H. Osterkamp, DDS</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>+12085438907</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>https://www.todaysdentalcarejerome.com/</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/TodaysDentalCareBuhlIdaho</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
         <is>
           <t>https://twitter.com/JeromeDentist</t>
         </is>
